--- a/frame.xlsx
+++ b/frame.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DACDT_2026\DANCDT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\test3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA56DB6-9152-4AF1-B837-44A3B72400C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282FD831-CCE4-4085-88CF-8122B530E770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="330" windowWidth="29040" windowHeight="15990" xr2:uid="{7E0444B2-CAAF-4140-9717-C34FF9FC2123}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -51,6 +50,93 @@
     <t>Giải thích</t>
   </si>
   <si>
+    <t>Positioning complete (END)</t>
+  </si>
+  <si>
+    <t>H100A</t>
+  </si>
+  <si>
+    <t>Dừng hẳn tại đích.</t>
+  </si>
+  <si>
+    <t>Continuous Positioning Control</t>
+  </si>
+  <si>
+    <t>H500A</t>
+  </si>
+  <si>
+    <t>Dừng 1 nhịp rồi chạy tiếp.</t>
+  </si>
+  <si>
+    <t>Continuous Path Control</t>
+  </si>
+  <si>
+    <t>HD00A</t>
+  </si>
+  <si>
+    <t>Chạy mượt liên tục không phanh.</t>
+  </si>
+  <si>
+    <t>H100F</t>
+  </si>
+  <si>
+    <t>H500F</t>
+  </si>
+  <si>
+    <t>HD00F</t>
+  </si>
+  <si>
+    <t>H1010</t>
+  </si>
+  <si>
+    <t>H5010</t>
+  </si>
+  <si>
+    <t>HD010</t>
+  </si>
+  <si>
+    <t>U0\G(2000 + (n - 1) * 10)</t>
+  </si>
+  <si>
+    <t>Move hex vào địa chỉ</t>
+  </si>
+  <si>
+    <t>n là số điểm đó</t>
+  </si>
+  <si>
+    <t>Vị trí</t>
+  </si>
+  <si>
+    <t>Tốc độ</t>
+  </si>
+  <si>
+    <t>Toạ độ tâm</t>
+  </si>
+  <si>
+    <t>Giá trị M code</t>
+  </si>
+  <si>
+    <t>Dwell (thời gian chờ)</t>
+  </si>
+  <si>
+    <t>U0\G(2000 + (n - 1) * 10+1)</t>
+  </si>
+  <si>
+    <t>U0\G(2000 + (n - 1) * 10+2)</t>
+  </si>
+  <si>
+    <t>U0\G(2000 + (n - 1) * 10+4)</t>
+  </si>
+  <si>
+    <t>U0\G(2000 + (n - 1) * 10+6)</t>
+  </si>
+  <si>
+    <t>U0\G(2000 + (n - 1) * 10+8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buffer </t>
+  </si>
+  <si>
     <r>
       <t>A. Chạy đường thẳng 2 trục</t>
     </r>
@@ -61,53 +147,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (ABS Linear 2 - Mã gốc: </t>
+      <t xml:space="preserve"> </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>0AH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Positioning complete (END)</t>
-  </si>
-  <si>
-    <t>H100A</t>
-  </si>
-  <si>
-    <t>Dừng hẳn tại đích.</t>
-  </si>
-  <si>
-    <t>Continuous Positioning Control</t>
-  </si>
-  <si>
-    <t>H500A</t>
-  </si>
-  <si>
-    <t>Dừng 1 nhịp rồi chạy tiếp.</t>
-  </si>
-  <si>
-    <t>Continuous Path Control</t>
-  </si>
-  <si>
-    <t>HD00A</t>
-  </si>
-  <si>
-    <t>Chạy mượt liên tục không phanh.</t>
   </si>
   <si>
     <r>
@@ -120,125 +161,18 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (ABS Circular CW - Mã gốc: </t>
+      <t xml:space="preserve"> </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>0FH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>H100F</t>
-  </si>
-  <si>
-    <t>H500F</t>
-  </si>
-  <si>
-    <t>HD00F</t>
-  </si>
-  <si>
-    <r>
-      <t>C. Chạy cung tròn ngược chiều kim đồng hồ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (ABS Circular CCW - Mã gốc: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF444746"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t>10H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>H1010</t>
-  </si>
-  <si>
-    <t>H5010</t>
-  </si>
-  <si>
-    <t>HD010</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10)</t>
-  </si>
-  <si>
-    <t>Move hex vào địa chỉ</t>
-  </si>
-  <si>
-    <t>n là số điểm đó</t>
-  </si>
-  <si>
-    <t>Vị trí</t>
-  </si>
-  <si>
-    <t>Tốc độ</t>
-  </si>
-  <si>
-    <t>Toạ độ tâm</t>
-  </si>
-  <si>
-    <t>Giá trị M code</t>
-  </si>
-  <si>
-    <t>Dwell (thời gian chờ)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+1)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+2)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+4)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+6)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buffer </t>
+  </si>
+  <si>
+    <t>C. Chạy cung tròn ngược chiều kim đồng hồ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,12 +191,6 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF444746"/>
-      <name val="Google Sans Text"/>
       <family val="2"/>
     </font>
     <font>
@@ -331,20 +259,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -353,18 +292,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -382,10 +309,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -709,220 +632,219 @@
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="80.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="18.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="80.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="9" t="s">
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D7" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="9" t="s">
+      <c r="C10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="D10" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="D13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="12" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="8" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="12" t="s">
+      <c r="B18" s="8"/>
+      <c r="C18" s="7" t="s">
         <v>31</v>
-      </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="12" t="s">
-        <v>34</v>
       </c>
       <c r="D18" s="1"/>
     </row>
@@ -941,6 +863,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b60d1cc7-9530-492f-a54f-9b2f7446c709" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x010100FE26EF9B520EC642848D5BAC3D4E65D3" ma:contentTypeVersion="12" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="330954201ec8980e1fa3f098ec994260">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b60d1cc7-9530-492f-a54f-9b2f7446c709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f00834c736c6b72a2deb67f0ac7b3a0b" ns3:_="">
     <xsd:import namespace="b60d1cc7-9530-492f-a54f-9b2f7446c709"/>
@@ -1134,14 +1064,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="b60d1cc7-9530-492f-a54f-9b2f7446c709" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1152,6 +1074,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCEFB804-6E9E-44D3-8E8C-99FA70A3493D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b60d1cc7-9530-492f-a54f-9b2f7446c709"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7B68156-F771-4DF3-A7D0-6804E807E2AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1169,22 +1107,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCEFB804-6E9E-44D3-8E8C-99FA70A3493D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b60d1cc7-9530-492f-a54f-9b2f7446c709"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D57045-E9DF-45DC-BF4E-E0EAEC22151B}">
   <ds:schemaRefs>

--- a/frame.xlsx
+++ b/frame.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New folder\test3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DACDT_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282FD831-CCE4-4085-88CF-8122B530E770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B8F01F-156F-4EEB-85BC-6A9F29CE64B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="330" windowWidth="29040" windowHeight="15990" xr2:uid="{7E0444B2-CAAF-4140-9717-C34FF9FC2123}"/>
+    <workbookView xWindow="2340" yWindow="2790" windowWidth="21600" windowHeight="11505" xr2:uid="{7E0444B2-CAAF-4140-9717-C34FF9FC2123}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <t>HD010</t>
   </si>
   <si>
-    <t>U0\G(2000 + (n - 1) * 10)</t>
-  </si>
-  <si>
     <t>Move hex vào địa chỉ</t>
   </si>
   <si>
@@ -117,21 +114,6 @@
   </si>
   <si>
     <t>Dwell (thời gian chờ)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+1)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+2)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+4)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+6)</t>
-  </si>
-  <si>
-    <t>U0\G(2000 + (n - 1) * 10+8)</t>
   </si>
   <si>
     <t xml:space="preserve">Buffer </t>
@@ -166,6 +148,24 @@
   </si>
   <si>
     <t>C. Chạy cung tròn ngược chiều kim đồng hồ</t>
+  </si>
+  <si>
+    <t>U0\G(A + (n - 1) * 10)</t>
+  </si>
+  <si>
+    <t>U0\G(A + (n - 1) * 10+1)</t>
+  </si>
+  <si>
+    <t>U0\G(A + (n - 1) * 10+2)</t>
+  </si>
+  <si>
+    <t>U0\G(A + (n - 1) * 10+4)</t>
+  </si>
+  <si>
+    <t>U0\G(A + (n - 1) * 10+6)</t>
+  </si>
+  <si>
+    <t>U0\G(A + (n - 1) * 10+8)</t>
   </si>
 </sst>
 </file>
@@ -660,7 +660,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>4</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>4</v>
@@ -736,7 +736,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>4</v>
@@ -782,69 +782,69 @@
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D18" s="1"/>
     </row>
@@ -871,6 +871,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Tài liệu" ma:contentTypeID="0x010100FE26EF9B520EC642848D5BAC3D4E65D3" ma:contentTypeVersion="12" ma:contentTypeDescription="Tạo tài liệu mới." ma:contentTypeScope="" ma:versionID="330954201ec8980e1fa3f098ec994260">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b60d1cc7-9530-492f-a54f-9b2f7446c709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f00834c736c6b72a2deb67f0ac7b3a0b" ns3:_="">
     <xsd:import namespace="b60d1cc7-9530-492f-a54f-9b2f7446c709"/>
@@ -1064,15 +1073,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCEFB804-6E9E-44D3-8E8C-99FA70A3493D}">
   <ds:schemaRefs>
@@ -1090,6 +1090,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D57045-E9DF-45DC-BF4E-E0EAEC22151B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7B68156-F771-4DF3-A7D0-6804E807E2AD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1105,12 +1113,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D57045-E9DF-45DC-BF4E-E0EAEC22151B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>